--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>52500</v>
+        <v>51800</v>
       </c>
       <c r="C419" t="n">
-        <v>4512009</v>
+        <v>5512028</v>
       </c>
       <c r="D419" t="n">
-        <v>47382</v>
+        <v>47397</v>
       </c>
       <c r="E419" t="n">
-        <v>49004</v>
+        <v>48994</v>
       </c>
       <c r="F419" t="n">
-        <v>51611</v>
+        <v>51327</v>
       </c>
       <c r="G419" t="n">
-        <v>49332</v>
+        <v>49240</v>
       </c>
       <c r="H419" t="n">
-        <v>0.770075349838536</v>
+        <v>0.7667743092931467</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>0.7667743092931467</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>52000</v>
+      </c>
+      <c r="C420" t="n">
+        <v>1525394</v>
+      </c>
+      <c r="D420" t="n">
+        <v>47694</v>
+      </c>
+      <c r="E420" t="n">
+        <v>49352</v>
+      </c>
+      <c r="F420" t="n">
+        <v>51482</v>
+      </c>
+      <c r="G420" t="n">
+        <v>49509</v>
+      </c>
+      <c r="H420" t="n">
+        <v>0.7764262648008611</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>51800</v>
+        <v>51200</v>
       </c>
       <c r="C421" t="n">
-        <v>460265</v>
+        <v>1508861</v>
       </c>
       <c r="D421" t="n">
-        <v>47829</v>
+        <v>47868</v>
       </c>
       <c r="E421" t="n">
-        <v>49383</v>
+        <v>49428</v>
       </c>
       <c r="F421" t="n">
-        <v>51584</v>
+        <v>51523</v>
       </c>
       <c r="G421" t="n">
-        <v>49599</v>
+        <v>49606</v>
       </c>
       <c r="H421" t="n">
-        <v>0.7796555435952637</v>
+        <v>0.7799067097237173</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>0.7799067097237173</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>49350</v>
+      </c>
+      <c r="C422" t="n">
+        <v>2139448</v>
+      </c>
+      <c r="D422" t="n">
+        <v>48018</v>
+      </c>
+      <c r="E422" t="n">
+        <v>49423</v>
+      </c>
+      <c r="F422" t="n">
+        <v>51237</v>
+      </c>
+      <c r="G422" t="n">
+        <v>49559</v>
+      </c>
+      <c r="H422" t="n">
+        <v>0.7782203085755293</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>0.7782203085755293</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C423" t="n">
+        <v>1490140</v>
+      </c>
+      <c r="D423" t="n">
+        <v>48206</v>
+      </c>
+      <c r="E423" t="n">
+        <v>49796</v>
+      </c>
+      <c r="F423" t="n">
+        <v>51100</v>
+      </c>
+      <c r="G423" t="n">
+        <v>49701</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0.7833153928955867</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>0.7833153928955867</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>47150</v>
+      </c>
+      <c r="C424" t="n">
+        <v>1563639</v>
+      </c>
+      <c r="D424" t="n">
+        <v>48531</v>
+      </c>
+      <c r="E424" t="n">
+        <v>49673</v>
+      </c>
+      <c r="F424" t="n">
+        <v>49880</v>
+      </c>
+      <c r="G424" t="n">
+        <v>49362</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0.7711517761033369</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>0.7711517761033369</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>47700</v>
+      </c>
+      <c r="C425" t="n">
+        <v>1747728</v>
+      </c>
+      <c r="D425" t="n">
+        <v>48886</v>
+      </c>
+      <c r="E425" t="n">
+        <v>49636</v>
+      </c>
+      <c r="F425" t="n">
+        <v>49047</v>
+      </c>
+      <c r="G425" t="n">
+        <v>49189</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0.7649443846429853</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>0.7649443846429853</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>47350</v>
+      </c>
+      <c r="C426" t="n">
+        <v>1010687</v>
+      </c>
+      <c r="D426" t="n">
+        <v>48863</v>
+      </c>
+      <c r="E426" t="n">
+        <v>49674</v>
+      </c>
+      <c r="F426" t="n">
+        <v>48422</v>
+      </c>
+      <c r="G426" t="n">
+        <v>48986</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0.7576605669178329</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>47750</v>
+      </c>
+      <c r="C427" t="n">
+        <v>1007463</v>
+      </c>
+      <c r="D427" t="n">
+        <v>48847</v>
+      </c>
+      <c r="E427" t="n">
+        <v>49796</v>
+      </c>
+      <c r="F427" t="n">
+        <v>48032</v>
+      </c>
+      <c r="G427" t="n">
+        <v>48892</v>
+      </c>
+      <c r="H427" t="n">
+        <v>0.7542877646214567</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>0.7542877646214567</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>48050</v>
+      </c>
+      <c r="C428" t="n">
+        <v>1146054</v>
+      </c>
+      <c r="D428" t="n">
+        <v>48986</v>
+      </c>
+      <c r="E428" t="n">
+        <v>50010</v>
+      </c>
+      <c r="F428" t="n">
+        <v>47582</v>
+      </c>
+      <c r="G428" t="n">
+        <v>48859</v>
+      </c>
+      <c r="H428" t="n">
+        <v>0.7531036957301758</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>0.7531036957301758</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>48600</v>
+      </c>
+      <c r="C429" t="n">
+        <v>1798600</v>
+      </c>
+      <c r="D429" t="n">
+        <v>49001</v>
+      </c>
+      <c r="E429" t="n">
+        <v>50012</v>
+      </c>
+      <c r="F429" t="n">
+        <v>47956</v>
+      </c>
+      <c r="G429" t="n">
+        <v>48990</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0.7578040904198062</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>0.7578040904198062</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>48250</v>
+      </c>
+      <c r="C430" t="n">
+        <v>1372151</v>
+      </c>
+      <c r="D430" t="n">
+        <v>48984</v>
+      </c>
+      <c r="E430" t="n">
+        <v>50020</v>
+      </c>
+      <c r="F430" t="n">
+        <v>48090</v>
+      </c>
+      <c r="G430" t="n">
+        <v>49032</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0.7593110871905275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>0.7593110871905275</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>46050</v>
+      </c>
+      <c r="C431" t="n">
+        <v>1743957</v>
+      </c>
+      <c r="D431" t="n">
+        <v>48897</v>
+      </c>
+      <c r="E431" t="n">
+        <v>49647</v>
+      </c>
+      <c r="F431" t="n">
+        <v>47693</v>
+      </c>
+      <c r="G431" t="n">
+        <v>48746</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0.749049156799426</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>0.749049156799426</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C432" t="n">
+        <v>1732695</v>
+      </c>
+      <c r="D432" t="n">
+        <v>48793</v>
+      </c>
+      <c r="E432" t="n">
+        <v>49401</v>
+      </c>
+      <c r="F432" t="n">
+        <v>47164</v>
+      </c>
+      <c r="G432" t="n">
+        <v>48453</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0.7385360602798707</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>0.7385360602798707</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>45400</v>
+      </c>
+      <c r="C433" t="n">
+        <v>1353592</v>
+      </c>
+      <c r="D433" t="n">
+        <v>48691</v>
+      </c>
+      <c r="E433" t="n">
+        <v>49167</v>
+      </c>
+      <c r="F433" t="n">
+        <v>46739</v>
+      </c>
+      <c r="G433" t="n">
+        <v>48199</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0.7294223179045569</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>0.7294223179045569</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>42200</v>
+      </c>
+      <c r="C434" t="n">
+        <v>1474036</v>
+      </c>
+      <c r="D434" t="n">
+        <v>48537</v>
+      </c>
+      <c r="E434" t="n">
+        <v>48763</v>
+      </c>
+      <c r="F434" t="n">
+        <v>45431</v>
+      </c>
+      <c r="G434" t="n">
+        <v>47577</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0.7071044133476856</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>0.7071044133476856</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>43600</v>
+      </c>
+      <c r="C435" t="n">
+        <v>1017183</v>
+      </c>
+      <c r="D435" t="n">
+        <v>48457</v>
+      </c>
+      <c r="E435" t="n">
+        <v>48521</v>
+      </c>
+      <c r="F435" t="n">
+        <v>44649</v>
+      </c>
+      <c r="G435" t="n">
+        <v>47209</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0.6939002511661285</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>0.6939002511661285</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>45300</v>
+      </c>
+      <c r="C436" t="n">
+        <v>816436</v>
+      </c>
+      <c r="D436" t="n">
+        <v>48425</v>
+      </c>
+      <c r="E436" t="n">
+        <v>47541</v>
+      </c>
+      <c r="F436" t="n">
+        <v>44350</v>
+      </c>
+      <c r="G436" t="n">
+        <v>46772</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0.6782203085755292</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>0.6782203085755292</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>43600</v>
+      </c>
+      <c r="C437" t="n">
+        <v>802276</v>
+      </c>
+      <c r="D437" t="n">
+        <v>48370</v>
+      </c>
+      <c r="E437" t="n">
+        <v>47416</v>
+      </c>
+      <c r="F437" t="n">
+        <v>43922</v>
+      </c>
+      <c r="G437" t="n">
+        <v>46569</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0.6709364908503768</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>0.6709364908503768</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>47700</v>
+      </c>
+      <c r="C438" t="n">
+        <v>2180775</v>
+      </c>
+      <c r="D438" t="n">
+        <v>48428</v>
+      </c>
+      <c r="E438" t="n">
+        <v>47170</v>
+      </c>
+      <c r="F438" t="n">
+        <v>44914</v>
+      </c>
+      <c r="G438" t="n">
+        <v>46837</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0.6805525654825977</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>0.6805525654825977</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>55400</v>
+      </c>
+      <c r="C439" t="n">
+        <v>11556314</v>
+      </c>
+      <c r="D439" t="n">
+        <v>49536</v>
+      </c>
+      <c r="E439" t="n">
+        <v>49646</v>
+      </c>
+      <c r="F439" t="n">
+        <v>52559</v>
+      </c>
+      <c r="G439" t="n">
+        <v>50580</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0.814854682454252</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>0.814854682454252</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>59800</v>
+      </c>
+      <c r="C440" t="n">
+        <v>12681459</v>
+      </c>
+      <c r="D440" t="n">
+        <v>51059</v>
+      </c>
+      <c r="E440" t="n">
+        <v>52429</v>
+      </c>
+      <c r="F440" t="n">
+        <v>56159</v>
+      </c>
+      <c r="G440" t="n">
+        <v>53216</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0.9094366702547543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>0.9094366702547543</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>59800</v>
+      </c>
+      <c r="C441" t="n">
+        <v>5404875</v>
+      </c>
+      <c r="D441" t="n">
+        <v>51829</v>
+      </c>
+      <c r="E441" t="n">
+        <v>53197</v>
+      </c>
+      <c r="F441" t="n">
+        <v>57034</v>
+      </c>
+      <c r="G441" t="n">
+        <v>54020</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0.9382848941514172</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>0.9382848941514172</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>62200</v>
+      </c>
+      <c r="C442" t="n">
+        <v>4620063</v>
+      </c>
+      <c r="D442" t="n">
+        <v>52419</v>
+      </c>
+      <c r="E442" t="n">
+        <v>53933</v>
+      </c>
+      <c r="F442" t="n">
+        <v>57985</v>
+      </c>
+      <c r="G442" t="n">
+        <v>54779</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0.965518478650879</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>0.965518478650879</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>64200</v>
+      </c>
+      <c r="C443" t="n">
+        <v>3967562</v>
+      </c>
+      <c r="D443" t="n">
+        <v>52988</v>
+      </c>
+      <c r="E443" t="n">
+        <v>54722</v>
+      </c>
+      <c r="F443" t="n">
+        <v>59217</v>
+      </c>
+      <c r="G443" t="n">
+        <v>55642</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0.9964836742016505</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>0.9964836742016505</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>62800</v>
+      </c>
+      <c r="C444" t="n">
+        <v>3259549</v>
+      </c>
+      <c r="D444" t="n">
+        <v>53327</v>
+      </c>
+      <c r="E444" t="n">
+        <v>55351</v>
+      </c>
+      <c r="F444" t="n">
+        <v>61080</v>
+      </c>
+      <c r="G444" t="n">
+        <v>56586</v>
+      </c>
+      <c r="H444" t="n">
+        <v>1.030355220667384</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성E&A_일별_기준주가.xlsx
+++ b/data/삼성E&A_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>1.030355220667384</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>61700</v>
+      </c>
+      <c r="C445" t="n">
+        <v>2202217</v>
+      </c>
+      <c r="D445" t="n">
+        <v>53518</v>
+      </c>
+      <c r="E445" t="n">
+        <v>55799</v>
+      </c>
+      <c r="F445" t="n">
+        <v>61985</v>
+      </c>
+      <c r="G445" t="n">
+        <v>57101</v>
+      </c>
+      <c r="H445" t="n">
+        <v>1.048833871546466</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
